--- a/Data_clean/MCAS/Estados_US/Edos_USA_2017/HAWAII_2017.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2017/HAWAII_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -545,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -573,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Topia</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -713,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -742,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C27">
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tultepec</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -871,7 +996,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C36">
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -998,7 +1158,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acatlán de Juárez</t>
+          <t>Acatlán De Juárez</t>
         </is>
       </c>
       <c r="C45">
@@ -1009,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C46">
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Juanacatlán</t>
@@ -1061,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C50">
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Mazamitla</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1113,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C54">
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1139,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C56">
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1165,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -1178,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1209,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -1222,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -1235,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -1248,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -1261,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1357,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1388,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -1401,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -1414,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1440,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1460,7 +1770,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C79">
@@ -1471,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Constancia del Rosario</t>
+          <t>Constancia Del Rosario</t>
         </is>
       </c>
       <c r="C80">
@@ -1484,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Andrés Cabecera Nueva</t>
@@ -1497,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>San Esteban Atatlahuca</t>
@@ -1510,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>San Juan Cieneguilla</t>
@@ -1523,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>San Martín Tilcajete</t>
@@ -1536,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>San Miguel el Grande</t>
+          <t>San Miguel El Grande</t>
         </is>
       </c>
       <c r="C85">
@@ -1549,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1562,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -1575,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1588,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1619,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1632,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1645,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C93">
@@ -1658,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1678,7 +2058,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C95">
@@ -1689,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1720,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1751,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -1764,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1795,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1826,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1857,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1888,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -1901,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1932,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1955,76 +2385,6 @@
       </c>
       <c r="D113">
         <v>1</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
